--- a/03_Features/01_Responsiveness/c_data/02_candidate_labels.xlsx
+++ b/03_Features/01_Responsiveness/c_data/02_candidate_labels.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t xml:space="preserve">label</t>
   </si>
@@ -87,6 +87,15 @@
     <t xml:space="preserve">fcsa_II</t>
   </si>
   <si>
+    <t xml:space="preserve">fcsa_mixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nfibre_mixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nfibre_I</t>
+  </si>
+  <si>
     <t xml:space="preserve">mcsa</t>
   </si>
   <si>
@@ -96,6 +105,9 @@
     <t xml:space="preserve">1rm_ext</t>
   </si>
   <si>
+    <t xml:space="preserve">volume_load</t>
+  </si>
+  <si>
     <t xml:space="preserve">n</t>
   </si>
   <si>
@@ -115,6 +127,24 @@
   </si>
   <si>
     <t xml:space="preserve">agreement_with_given</t>
+  </si>
+  <si>
+    <t xml:space="preserve">partition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shares_partition_with</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">fcsa_II, fcsa_mixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fcsa_I, fcsa_II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fcsa_I, fcsa_mixed</t>
   </si>
 </sst>
 </file>
@@ -990,7 +1020,7 @@
         <v>4</v>
       </c>
       <c r="C50" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -1012,7 +1042,7 @@
         <v>7</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -1067,7 +1097,7 @@
         <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58">
@@ -1089,7 +1119,7 @@
         <v>15</v>
       </c>
       <c r="C59" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -1122,7 +1152,7 @@
         <v>18</v>
       </c>
       <c r="C62" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63">
@@ -1155,7 +1185,7 @@
         <v>21</v>
       </c>
       <c r="C65" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66">
@@ -1166,7 +1196,7 @@
         <v>4</v>
       </c>
       <c r="C66" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67">
@@ -1177,7 +1207,7 @@
         <v>6</v>
       </c>
       <c r="C67" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68">
@@ -1199,7 +1229,7 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -1232,7 +1262,7 @@
         <v>11</v>
       </c>
       <c r="C72" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73">
@@ -1265,7 +1295,7 @@
         <v>15</v>
       </c>
       <c r="C75" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76">
@@ -1276,7 +1306,7 @@
         <v>16</v>
       </c>
       <c r="C76" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -1298,7 +1328,7 @@
         <v>18</v>
       </c>
       <c r="C78" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -1320,7 +1350,7 @@
         <v>20</v>
       </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -1353,7 +1383,7 @@
         <v>6</v>
       </c>
       <c r="C83" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="84">
@@ -1372,7 +1402,7 @@
         <v>26</v>
       </c>
       <c r="B85" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C85" t="s">
         <v>5</v>
@@ -1383,10 +1413,10 @@
         <v>26</v>
       </c>
       <c r="B86" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C86" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87">
@@ -1394,7 +1424,7 @@
         <v>26</v>
       </c>
       <c r="B87" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
@@ -1405,10 +1435,10 @@
         <v>26</v>
       </c>
       <c r="B88" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="89">
@@ -1416,10 +1446,10 @@
         <v>26</v>
       </c>
       <c r="B89" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C89" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
@@ -1427,7 +1457,7 @@
         <v>26</v>
       </c>
       <c r="B90" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C90" t="s">
         <v>5</v>
@@ -1438,7 +1468,7 @@
         <v>26</v>
       </c>
       <c r="B91" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C91" t="s">
         <v>14</v>
@@ -1449,10 +1479,10 @@
         <v>26</v>
       </c>
       <c r="B92" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C92" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -1460,7 +1490,7 @@
         <v>26</v>
       </c>
       <c r="B93" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C93" t="s">
         <v>5</v>
@@ -1471,10 +1501,10 @@
         <v>26</v>
       </c>
       <c r="B94" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C94" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
@@ -1482,10 +1512,10 @@
         <v>26</v>
       </c>
       <c r="B95" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C95" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="96">
@@ -1493,10 +1523,714 @@
         <v>26</v>
       </c>
       <c r="B96" t="s">
+        <v>20</v>
+      </c>
+      <c r="C96" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>26</v>
+      </c>
+      <c r="B97" t="s">
         <v>21</v>
       </c>
-      <c r="C96" t="s">
-        <v>14</v>
+      <c r="C97" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>27</v>
+      </c>
+      <c r="B98" t="s">
+        <v>4</v>
+      </c>
+      <c r="C98" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>27</v>
+      </c>
+      <c r="B99" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>27</v>
+      </c>
+      <c r="B100" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>27</v>
+      </c>
+      <c r="B101" t="s">
+        <v>8</v>
+      </c>
+      <c r="C101" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>27</v>
+      </c>
+      <c r="B102" t="s">
+        <v>9</v>
+      </c>
+      <c r="C102" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>27</v>
+      </c>
+      <c r="B103" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>27</v>
+      </c>
+      <c r="B104" t="s">
+        <v>11</v>
+      </c>
+      <c r="C104" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>27</v>
+      </c>
+      <c r="B105" t="s">
+        <v>12</v>
+      </c>
+      <c r="C105" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>27</v>
+      </c>
+      <c r="B106" t="s">
+        <v>13</v>
+      </c>
+      <c r="C106" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>27</v>
+      </c>
+      <c r="B107" t="s">
+        <v>15</v>
+      </c>
+      <c r="C107" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>27</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>27</v>
+      </c>
+      <c r="B109" t="s">
+        <v>17</v>
+      </c>
+      <c r="C109" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>27</v>
+      </c>
+      <c r="B110" t="s">
+        <v>18</v>
+      </c>
+      <c r="C110" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>27</v>
+      </c>
+      <c r="B111" t="s">
+        <v>19</v>
+      </c>
+      <c r="C111" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>27</v>
+      </c>
+      <c r="B112" t="s">
+        <v>20</v>
+      </c>
+      <c r="C112" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>27</v>
+      </c>
+      <c r="B113" t="s">
+        <v>21</v>
+      </c>
+      <c r="C113" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>28</v>
+      </c>
+      <c r="B114" t="s">
+        <v>4</v>
+      </c>
+      <c r="C114" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>28</v>
+      </c>
+      <c r="B115" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>28</v>
+      </c>
+      <c r="B116" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>28</v>
+      </c>
+      <c r="B117" t="s">
+        <v>8</v>
+      </c>
+      <c r="C117" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>28</v>
+      </c>
+      <c r="B118" t="s">
+        <v>9</v>
+      </c>
+      <c r="C118" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>28</v>
+      </c>
+      <c r="B119" t="s">
+        <v>10</v>
+      </c>
+      <c r="C119" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>28</v>
+      </c>
+      <c r="B120" t="s">
+        <v>11</v>
+      </c>
+      <c r="C120" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>28</v>
+      </c>
+      <c r="B121" t="s">
+        <v>12</v>
+      </c>
+      <c r="C121" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>28</v>
+      </c>
+      <c r="B122" t="s">
+        <v>13</v>
+      </c>
+      <c r="C122" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>28</v>
+      </c>
+      <c r="B123" t="s">
+        <v>15</v>
+      </c>
+      <c r="C123" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>28</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>28</v>
+      </c>
+      <c r="B125" t="s">
+        <v>17</v>
+      </c>
+      <c r="C125" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>28</v>
+      </c>
+      <c r="B126" t="s">
+        <v>18</v>
+      </c>
+      <c r="C126" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>28</v>
+      </c>
+      <c r="B127" t="s">
+        <v>19</v>
+      </c>
+      <c r="C127" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>28</v>
+      </c>
+      <c r="B128" t="s">
+        <v>20</v>
+      </c>
+      <c r="C128" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>28</v>
+      </c>
+      <c r="B129" t="s">
+        <v>21</v>
+      </c>
+      <c r="C129" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>29</v>
+      </c>
+      <c r="B130" t="s">
+        <v>4</v>
+      </c>
+      <c r="C130" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>29</v>
+      </c>
+      <c r="B131" t="s">
+        <v>6</v>
+      </c>
+      <c r="C131" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>29</v>
+      </c>
+      <c r="B132" t="s">
+        <v>7</v>
+      </c>
+      <c r="C132" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>29</v>
+      </c>
+      <c r="B133" t="s">
+        <v>9</v>
+      </c>
+      <c r="C133" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>29</v>
+      </c>
+      <c r="B134" t="s">
+        <v>10</v>
+      </c>
+      <c r="C134" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>29</v>
+      </c>
+      <c r="B135" t="s">
+        <v>11</v>
+      </c>
+      <c r="C135" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>29</v>
+      </c>
+      <c r="B136" t="s">
+        <v>12</v>
+      </c>
+      <c r="C136" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>29</v>
+      </c>
+      <c r="B137" t="s">
+        <v>13</v>
+      </c>
+      <c r="C137" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>29</v>
+      </c>
+      <c r="B138" t="s">
+        <v>15</v>
+      </c>
+      <c r="C138" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>29</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>29</v>
+      </c>
+      <c r="B140" t="s">
+        <v>17</v>
+      </c>
+      <c r="C140" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>29</v>
+      </c>
+      <c r="B141" t="s">
+        <v>18</v>
+      </c>
+      <c r="C141" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>29</v>
+      </c>
+      <c r="B142" t="s">
+        <v>19</v>
+      </c>
+      <c r="C142" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>29</v>
+      </c>
+      <c r="B143" t="s">
+        <v>20</v>
+      </c>
+      <c r="C143" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>29</v>
+      </c>
+      <c r="B144" t="s">
+        <v>21</v>
+      </c>
+      <c r="C144" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>30</v>
+      </c>
+      <c r="B145" t="s">
+        <v>4</v>
+      </c>
+      <c r="C145" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>30</v>
+      </c>
+      <c r="B146" t="s">
+        <v>6</v>
+      </c>
+      <c r="C146" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>30</v>
+      </c>
+      <c r="B147" t="s">
+        <v>7</v>
+      </c>
+      <c r="C147" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>30</v>
+      </c>
+      <c r="B148" t="s">
+        <v>8</v>
+      </c>
+      <c r="C148" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>30</v>
+      </c>
+      <c r="B149" t="s">
+        <v>9</v>
+      </c>
+      <c r="C149" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>30</v>
+      </c>
+      <c r="B150" t="s">
+        <v>10</v>
+      </c>
+      <c r="C150" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>30</v>
+      </c>
+      <c r="B151" t="s">
+        <v>11</v>
+      </c>
+      <c r="C151" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>30</v>
+      </c>
+      <c r="B152" t="s">
+        <v>12</v>
+      </c>
+      <c r="C152" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>30</v>
+      </c>
+      <c r="B153" t="s">
+        <v>13</v>
+      </c>
+      <c r="C153" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>30</v>
+      </c>
+      <c r="B154" t="s">
+        <v>15</v>
+      </c>
+      <c r="C154" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>30</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>30</v>
+      </c>
+      <c r="B156" t="s">
+        <v>17</v>
+      </c>
+      <c r="C156" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>30</v>
+      </c>
+      <c r="B157" t="s">
+        <v>18</v>
+      </c>
+      <c r="C157" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>30</v>
+      </c>
+      <c r="B158" t="s">
+        <v>19</v>
+      </c>
+      <c r="C158" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>30</v>
+      </c>
+      <c r="B159" t="s">
+        <v>20</v>
+      </c>
+      <c r="C159" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>30</v>
+      </c>
+      <c r="B160" t="s">
+        <v>21</v>
+      </c>
+      <c r="C160" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1515,25 +2249,31 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H1" t="s">
-        <v>33</v>
+        <v>37</v>
+      </c>
+      <c r="I1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="2">
@@ -1561,6 +2301,12 @@
       <c r="H2" t="n">
         <v>1</v>
       </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
@@ -1587,10 +2333,16 @@
       <c r="H3" t="n">
         <v>0.53125</v>
       </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" t="n">
         <v>16</v>
@@ -1602,10 +2354,10 @@
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.829021879743861</v>
+        <v>0.835177563982897</v>
       </c>
       <c r="F4" t="n">
-        <v>0.687277277094045</v>
+        <v>0.697521563380406</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
@@ -1613,10 +2365,16 @@
       <c r="H4" t="n">
         <v>0.53125</v>
       </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>16</v>
@@ -1628,16 +2386,22 @@
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.496807795570891</v>
+        <v>0.829021879743861</v>
       </c>
       <c r="F5" t="n">
-        <v>0.246817985740008</v>
+        <v>0.687277277094045</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.196428571428571</v>
+        <v>0.53125</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -1654,16 +2418,22 @@
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.273744611777964</v>
+        <v>-0.600282058411429</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0749361124774681</v>
+        <v>0.360338549650662</v>
       </c>
       <c r="G6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0714285714285714</v>
+        <v>0.196428571428571</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -1671,25 +2441,159 @@
         <v>26</v>
       </c>
       <c r="B7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.489823092226803</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.239926661678627</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.196428571428571</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="n">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.496807795570891</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.246817985740008</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.196428571428571</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.273744611777964</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0749361124774681</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.0714285714285714</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="n">
         <v>15</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C10" t="n">
         <v>7</v>
       </c>
-      <c r="D7" t="n">
-        <v>8</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="n">
         <v>0.127677047329517</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F10" t="n">
         <v>0.0163014284147838</v>
       </c>
-      <c r="G7" t="b">
+      <c r="G10" t="b">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H10" t="n">
         <v>-0.0331632653061225</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0433581560331737</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.00187992969459705</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.0714285714285714</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
